--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/2mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/2mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.62476664352</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>411.3469079824853</v>
       </c>
-      <c r="W2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
+      <c r="W2" t="s">
+        <v>29</v>
+      </c>
       <c r="X2">
-        <v>416.1320821313182</v>
+        <v>0.255571216</v>
+      </c>
+      <c r="Y2">
+        <v>0.263000284</v>
+      </c>
+      <c r="Z2">
+        <v>0.3667230505869508</v>
+      </c>
+      <c r="AA2">
+        <v>3.714533999999993</v>
+      </c>
+      <c r="AB2">
+        <v>0.09923168662355218</v>
+      </c>
+      <c r="AC2">
+        <v>40.81864746648514</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.62488238426</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>411.9286454618021</v>
       </c>
-      <c r="W3" t="b">
+      <c r="V3" t="b">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>415.9881872374526</v>
+      </c>
+      <c r="X3">
+        <v>0.255571534</v>
+      </c>
+      <c r="Y3">
+        <v>0.262982138</v>
+      </c>
+      <c r="Z3">
+        <v>0.3667102587850035</v>
+      </c>
+      <c r="AA3">
+        <v>3.705302000000003</v>
+      </c>
+      <c r="AB3">
+        <v>0.0994729862244178</v>
+      </c>
+      <c r="AC3">
+        <v>40.97577247546492</v>
+      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.6249987037</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>411.5057336808538</v>
       </c>
-      <c r="V4">
-        <v>0.3006932190148026</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.255575668</v>
+      </c>
+      <c r="Y4">
+        <v>0.26298341</v>
+      </c>
+      <c r="Z4">
+        <v>0.3667140521017354</v>
+      </c>
+      <c r="AA4">
+        <v>3.703871000000007</v>
+      </c>
+      <c r="AB4">
+        <v>0.0995120485059182</v>
+      </c>
+      <c r="AC4">
+        <v>40.94977853051258</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.62511444445</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>411.7438197665874</v>
       </c>
-      <c r="V5">
-        <v>0.2120141097098774</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>40.97060652048611</v>
+      </c>
+      <c r="X5">
+        <v>0.255584574</v>
+      </c>
+      <c r="Y5">
+        <v>0.262986276</v>
+      </c>
+      <c r="Z5">
+        <v>0.3667223143348515</v>
+      </c>
+      <c r="AA5">
+        <v>3.700851</v>
+      </c>
+      <c r="AB5">
+        <v>0.09959465471768114</v>
+      </c>
+      <c r="AC5">
+        <v>41.00748356179241</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.62523076389</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>411.914951732937</v>
       </c>
-      <c r="V6">
-        <v>0.2055198888499592</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.255575668</v>
+      </c>
+      <c r="Y6">
+        <v>0.262972586</v>
+      </c>
+      <c r="Z6">
+        <v>0.3667062899122043</v>
+      </c>
+      <c r="AA6">
+        <v>3.698459000000007</v>
+      </c>
+      <c r="AB6">
+        <v>0.09965410810201189</v>
+      </c>
+      <c r="AC6">
+        <v>41.04901712882911</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.62534708333</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>412.0474053135742</v>
       </c>
-      <c r="V7">
-        <v>0.152202871890109</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.255558814</v>
+      </c>
+      <c r="Y7">
+        <v>0.26296208</v>
+      </c>
+      <c r="Z7">
+        <v>0.3666870094931275</v>
+      </c>
+      <c r="AA7">
+        <v>3.701633000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.09956433726315077</v>
+      </c>
+      <c r="AC7">
+        <v>41.02522683104689</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.62546282407</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>411.4013806721546</v>
       </c>
-      <c r="V8">
-        <v>0.341234773242263</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.25554005</v>
+      </c>
+      <c r="Y8">
+        <v>0.262947754</v>
+      </c>
+      <c r="Z8">
+        <v>0.3666636585314217</v>
+      </c>
+      <c r="AA8">
+        <v>3.703852000000005</v>
+      </c>
+      <c r="AB8">
+        <v>0.09949901698852655</v>
+      </c>
+      <c r="AC8">
+        <v>40.93403296460198</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.62557856482</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>412.9211466639711</v>
       </c>
-      <c r="V9">
-        <v>0.7627210558909905</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0.255514608</v>
+      </c>
+      <c r="Y9">
+        <v>0.262940432</v>
+      </c>
+      <c r="Z9">
+        <v>0.366640676523678</v>
+      </c>
+      <c r="AA9">
+        <v>3.712912000000003</v>
+      </c>
+      <c r="AB9">
+        <v>0.09925252325999746</v>
+      </c>
+      <c r="AC9">
+        <v>40.98346571381062</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.62569430556</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>412.7372893660746</v>
       </c>
-      <c r="V10">
-        <v>0.8294721428276872</v>
-      </c>
-      <c r="W10" t="b">
-        <v>1</v>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0.255505702</v>
+      </c>
+      <c r="Y10">
+        <v>0.262932472</v>
+      </c>
+      <c r="Z10">
+        <v>0.3666287612647753</v>
+      </c>
+      <c r="AA10">
+        <v>3.713385000000002</v>
+      </c>
+      <c r="AB10">
+        <v>0.09923681671149863</v>
+      </c>
+      <c r="AC10">
+        <v>40.95873473482192</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.625810625</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>413.3230891221648</v>
       </c>
-      <c r="V11">
-        <v>0.2995893300068592</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0.255500614</v>
+      </c>
+      <c r="Y11">
+        <v>0.26293311</v>
+      </c>
+      <c r="Z11">
+        <v>0.3666256729808335</v>
+      </c>
+      <c r="AA11">
+        <v>3.716248</v>
+      </c>
+      <c r="AB11">
+        <v>0.09916031443627246</v>
+      </c>
+      <c r="AC11">
+        <v>40.98524748112533</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.62592694444</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>412.6847201677273</v>
       </c>
-      <c r="V12">
-        <v>0.3543632309837959</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0.25548853</v>
+      </c>
+      <c r="Y12">
+        <v>0.26292515</v>
+      </c>
+      <c r="Z12">
+        <v>0.3666115430044223</v>
+      </c>
+      <c r="AA12">
+        <v>3.718310000000002</v>
+      </c>
+      <c r="AB12">
+        <v>0.09910210347602036</v>
+      </c>
+      <c r="AC12">
+        <v>40.89792384103462</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.62604268519</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>414.0080606559209</v>
       </c>
-      <c r="V13">
-        <v>0.6618069924756529</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0.255484078</v>
+      </c>
+      <c r="Y13">
+        <v>0.26292515</v>
+      </c>
+      <c r="Z13">
+        <v>0.3666084404566166</v>
+      </c>
+      <c r="AA13">
+        <v>3.720536000000003</v>
+      </c>
+      <c r="AB13">
+        <v>0.09904258486313708</v>
+      </c>
+      <c r="AC13">
+        <v>41.00442848153685</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.62615900463</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>411.635304692722</v>
       </c>
-      <c r="V14">
-        <v>1.189010355139156</v>
-      </c>
-      <c r="W14" t="b">
-        <v>1</v>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0.255478034</v>
+      </c>
+      <c r="Y14">
+        <v>0.26291369</v>
+      </c>
+      <c r="Z14">
+        <v>0.366596009588104</v>
+      </c>
+      <c r="AA14">
+        <v>3.717828000000004</v>
+      </c>
+      <c r="AB14">
+        <v>0.09911066404627519</v>
+      </c>
+      <c r="AC14">
+        <v>40.7974483929865</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.62627474537</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>413.8297638294677</v>
       </c>
-      <c r="V15">
-        <v>1.321451949061185</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.255469448</v>
+      </c>
+      <c r="Y15">
+        <v>0.26290955</v>
+      </c>
+      <c r="Z15">
+        <v>0.366587056976412</v>
+      </c>
+      <c r="AA15">
+        <v>3.720050999999998</v>
+      </c>
+      <c r="AB15">
+        <v>0.09904964706965631</v>
+      </c>
+      <c r="AC15">
+        <v>40.98969205422799</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.62639106481</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>414.0130471141226</v>
       </c>
-      <c r="V16">
-        <v>1.323058495041462</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.255464678</v>
+      </c>
+      <c r="Y16">
+        <v>0.262912416</v>
+      </c>
+      <c r="Z16">
+        <v>0.3665857883123686</v>
+      </c>
+      <c r="AA16">
+        <v>3.723868999999993</v>
+      </c>
+      <c r="AB16">
+        <v>0.09894879037178671</v>
+      </c>
+      <c r="AC16">
+        <v>40.96609021007998</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.62650680556</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>415.3315723769355</v>
       </c>
-      <c r="V17">
-        <v>0.8193015871620535</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.255463406</v>
+      </c>
+      <c r="Y17">
+        <v>0.262916554</v>
+      </c>
+      <c r="Z17">
+        <v>0.3665878696470408</v>
+      </c>
+      <c r="AA17">
+        <v>3.726573999999999</v>
+      </c>
+      <c r="AB17">
+        <v>0.09887825612376494</v>
+      </c>
+      <c r="AC17">
+        <v>41.06726158977264</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.6266225463</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>415.2978915959854</v>
       </c>
-      <c r="V18">
-        <v>0.7517167691641167</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.255457364</v>
+      </c>
+      <c r="Y18">
+        <v>0.262916236</v>
+      </c>
+      <c r="Z18">
+        <v>0.3665834311234432</v>
+      </c>
+      <c r="AA18">
+        <v>3.729436</v>
+      </c>
+      <c r="AB18">
+        <v>0.09880196852111432</v>
+      </c>
+      <c r="AC18">
+        <v>41.03224921235169</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.62673886574</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>414.5818740610621</v>
       </c>
-      <c r="V19">
-        <v>0.4234507193183533</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.255448458</v>
+      </c>
+      <c r="Y19">
+        <v>0.262917192</v>
+      </c>
+      <c r="Z19">
+        <v>0.3665779106052936</v>
+      </c>
+      <c r="AA19">
+        <v>3.734366999999999</v>
+      </c>
+      <c r="AB19">
+        <v>0.09867137328383446</v>
+      </c>
+      <c r="AC19">
+        <v>40.90736285219071</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.62685460648</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>414.6396185001242</v>
       </c>
-      <c r="V20">
-        <v>0.3977727574247913</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.255446232</v>
+      </c>
+      <c r="Y20">
+        <v>0.262916236</v>
+      </c>
+      <c r="Z20">
+        <v>0.3665756737638295</v>
+      </c>
+      <c r="AA20">
+        <v>3.735002000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.09865417435383976</v>
+      </c>
+      <c r="AC20">
+        <v>40.90592921752086</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.62697092593</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>416.5062017718307</v>
       </c>
-      <c r="V21">
-        <v>1.094722542389146</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.255442098</v>
+      </c>
+      <c r="Y21">
+        <v>0.262920694</v>
+      </c>
+      <c r="Z21">
+        <v>0.3665759904359303</v>
+      </c>
+      <c r="AA21">
+        <v>3.739297999999998</v>
+      </c>
+      <c r="AB21">
+        <v>0.09854208213446254</v>
+      </c>
+      <c r="AC21">
+        <v>41.04338834451276</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.62708724537</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>416.2250951708503</v>
       </c>
-      <c r="V22">
-        <v>1.006387127695492</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.255435738</v>
+      </c>
+      <c r="Y22">
+        <v>0.26292515</v>
+      </c>
+      <c r="Z22">
+        <v>0.366574754654664</v>
+      </c>
+      <c r="AA22">
+        <v>3.744706000000001</v>
+      </c>
+      <c r="AB22">
+        <v>0.09840090869514888</v>
+      </c>
+      <c r="AC22">
+        <v>40.95692758653649</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.62720356481</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>416.6625728817392</v>
       </c>
-      <c r="V23">
-        <v>0.2216828036687098</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.255433512</v>
+      </c>
+      <c r="Y23">
+        <v>0.262931836</v>
+      </c>
+      <c r="Z23">
+        <v>0.3665779991147655</v>
+      </c>
+      <c r="AA23">
+        <v>3.749162000000005</v>
+      </c>
+      <c r="AB23">
+        <v>0.09828602549031287</v>
+      </c>
+      <c r="AC23">
+        <v>40.95210825911396</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.62731988426</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>416.3091720458394</v>
       </c>
-      <c r="V24">
-        <v>0.2321450047019346</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
+      <c r="X24">
+        <v>0.255427152</v>
+      </c>
+      <c r="Y24">
+        <v>0.262934382</v>
+      </c>
+      <c r="Z24">
+        <v>0.3665753936321327</v>
+      </c>
+      <c r="AA24">
+        <v>3.753614999999996</v>
+      </c>
+      <c r="AB24">
+        <v>0.09816994371731154</v>
+      </c>
+      <c r="AC24">
+        <v>40.86904798874063</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.627435625</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>416.7237899353461</v>
       </c>
-      <c r="V25">
-        <v>0.2238108102718196</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
+      <c r="X25">
+        <v>0.255428424</v>
+      </c>
+      <c r="Y25">
+        <v>0.262938204</v>
+      </c>
+      <c r="Z25">
+        <v>0.3665790213717492</v>
+      </c>
+      <c r="AA25">
+        <v>3.754889999999996</v>
+      </c>
+      <c r="AB25">
+        <v>0.09813791645818136</v>
+      </c>
+      <c r="AC25">
+        <v>40.89640448281172</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.62755194445</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>416.6900987635029</v>
       </c>
-      <c r="V26">
-        <v>0.2302709467816284</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
+      <c r="X26">
+        <v>0.255444642</v>
+      </c>
+      <c r="Y26">
+        <v>0.262947436</v>
+      </c>
+      <c r="Z26">
+        <v>0.366596943829981</v>
+      </c>
+      <c r="AA26">
+        <v>3.751396999999997</v>
+      </c>
+      <c r="AB26">
+        <v>0.09823309898637871</v>
+      </c>
+      <c r="AC26">
+        <v>40.9327597184791</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.62766826389</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>417.5443001545235</v>
       </c>
-      <c r="V27">
-        <v>0.4837410001328751</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
+      <c r="X27">
+        <v>0.255453548</v>
+      </c>
+      <c r="Y27">
+        <v>0.262952848</v>
+      </c>
+      <c r="Z27">
+        <v>0.366607031379786</v>
+      </c>
+      <c r="AA27">
+        <v>3.749650000000003</v>
+      </c>
+      <c r="AB27">
+        <v>0.09828106890511819</v>
+      </c>
+      <c r="AC27">
+        <v>41.03670013442608</v>
+      </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.62778458333</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>417.0597773231411</v>
       </c>
-      <c r="V28">
-        <v>0.4283854627181728</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
+      <c r="X28">
+        <v>0.255460544</v>
+      </c>
+      <c r="Y28">
+        <v>0.262962398</v>
+      </c>
+      <c r="Z28">
+        <v>0.3666187560705075</v>
+      </c>
+      <c r="AA28">
+        <v>3.750926999999997</v>
+      </c>
+      <c r="AB28">
+        <v>0.09825106523675295</v>
+      </c>
+      <c r="AC28">
+        <v>40.97656738940159</v>
+      </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.62790090278</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>417.5130549383018</v>
       </c>
-      <c r="V29">
-        <v>0.2711700678154979</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
       </c>
+      <c r="X29">
+        <v>0.25546436</v>
+      </c>
+      <c r="Y29">
+        <v>0.262963036</v>
+      </c>
+      <c r="Z29">
+        <v>0.3666218726870328</v>
+      </c>
+      <c r="AA29">
+        <v>3.749338000000002</v>
+      </c>
+      <c r="AB29">
+        <v>0.09829310050854091</v>
+      </c>
+      <c r="AC29">
+        <v>41.03865267267846</v>
+      </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.62801722223</v>
       </c>
@@ -2547,11 +3018,26 @@
       <c r="U30">
         <v>416.8831653364682</v>
       </c>
-      <c r="V30">
-        <v>0.3249136553869387</v>
-      </c>
-      <c r="W30" t="b">
+      <c r="V30" t="b">
         <v>1</v>
+      </c>
+      <c r="X30">
+        <v>0.25546754</v>
+      </c>
+      <c r="Y30">
+        <v>0.262969722</v>
+      </c>
+      <c r="Z30">
+        <v>0.366628884135455</v>
+      </c>
+      <c r="AA30">
+        <v>3.751091000000002</v>
+      </c>
+      <c r="AB30">
+        <v>0.09824950014922142</v>
+      </c>
+      <c r="AC30">
+        <v>40.95856261493322</v>
       </c>
     </row>
   </sheetData>
